--- a/artfynd/A 54592-2023 artfynd.xlsx
+++ b/artfynd/A 54592-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 54592-2023 artfynd.xlsx
+++ b/artfynd/A 54592-2023 artfynd.xlsx
@@ -675,53 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>57194961</v>
+        <v>89125228</v>
       </c>
       <c r="B2" t="n">
-        <v>96926</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222295</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Latourr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gålsjö 4050/8550, Nrk</t>
+          <t>Gålsjö, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>504924.1262494169</v>
+        <v>504935</v>
       </c>
       <c r="R2" t="n">
-        <v>6531846.866549347</v>
+        <v>6531860</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1981-05-26</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-11-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1981-05-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-11-05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,44 +765,39 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Gunnar Hallin</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Gunnar Hallin</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>59870517</v>
+        <v>62431589</v>
       </c>
       <c r="B3" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220785</v>
+        <v>220299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -827,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504924.1262494169</v>
+        <v>504924</v>
       </c>
       <c r="R3" t="n">
-        <v>6531846.866549347</v>
+        <v>6531847</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -860,19 +845,9 @@
           <t>1981-05-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1981-05-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,32 +874,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>62431589</v>
+        <v>59870517</v>
       </c>
       <c r="B4" t="n">
-        <v>106964</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220299</v>
+        <v>220785</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -939,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>504924.1262494169</v>
+        <v>504924</v>
       </c>
       <c r="R4" t="n">
-        <v>6531846.866549347</v>
+        <v>6531847</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -972,19 +942,9 @@
           <t>1981-05-26</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1981-05-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89125228</v>
+        <v>57194961</v>
       </c>
       <c r="B5" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99754</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,42 +982,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>222295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vårstarr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carex caryophyllea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Latourr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gålsjö, Nrk</t>
+          <t>Gålsjö 4050/8550, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504934.9710228583</v>
+        <v>504924</v>
       </c>
       <c r="R5" t="n">
-        <v>6531859.787388684</v>
+        <v>6531847</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,22 +1036,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-11-05</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1981-05-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-11-05</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1981-05-26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,12 +1056,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Gunnar Hallin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Gunnar Hallin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 54592-2023 artfynd.xlsx
+++ b/artfynd/A 54592-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89125228</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62431589</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59870517</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,8 +1085,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57194961</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>